--- a/assets/templates/┘ç┘è┘â┘ä ╪º┘ä╪¡┘à┘ä┘ç.xlsx
+++ b/assets/templates/┘ç┘è┘â┘ä ╪º┘ä╪¡┘à┘ä┘ç.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MZJ\content\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrahm\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2898B4F-C99C-479E-A8B8-6BA19F6EDB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B37DAC-D6AF-4F99-A382-CCC41B7FDDED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="9" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="34">
   <si>
     <t>العنصر</t>
   </si>
@@ -105,9 +105,6 @@
     <t>الترجمة التنفيذية لإحساس الحملة</t>
   </si>
   <si>
-    <t xml:space="preserve">campaign logic </t>
-  </si>
-  <si>
     <t>قواعد كتابة المحتوى</t>
   </si>
   <si>
@@ -117,9 +114,6 @@
     <t>حمله - CA01</t>
   </si>
   <si>
-    <t xml:space="preserve">                                                                                                                                                                                                                                                </t>
-  </si>
-  <si>
     <t>التوجيه الاستراتيجي الثابت</t>
   </si>
   <si>
@@ -139,6 +133,9 @@
   </si>
   <si>
     <t xml:space="preserve">اسم المحتوي </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                                                                               campaign logic                                                                                                                                                                 </t>
   </si>
 </sst>
 </file>
@@ -240,7 +237,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -433,17 +430,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -513,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -542,24 +528,12 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -572,30 +546,30 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -656,7 +630,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -946,358 +920,356 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3AF20D0-00CE-4E98-AA63-4505C115A064}">
   <dimension ref="A1:K39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.6640625" customWidth="1"/>
-    <col min="3" max="3" width="112.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6640625" customWidth="1"/>
-    <col min="5" max="5" width="26.33203125" customWidth="1"/>
-    <col min="6" max="7" width="20.88671875" customWidth="1"/>
-    <col min="8" max="8" width="42.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="112.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="26.28515625" customWidth="1"/>
+    <col min="6" max="7" width="20.85546875" customWidth="1"/>
+    <col min="8" max="8" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="37"/>
-    </row>
-    <row r="2" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="49" t="s">
-        <v>27</v>
+    <row r="1" spans="1:3" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="33"/>
+    </row>
+    <row r="2" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="45" t="s">
+        <v>33</v>
       </c>
       <c r="B2" s="9" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="5"/>
     </row>
-    <row r="3" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="49"/>
+    <row r="3" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="45"/>
       <c r="B3" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="5"/>
     </row>
-    <row r="4" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="50"/>
+    <row r="4" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="45"/>
       <c r="B4" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="5"/>
     </row>
-    <row r="5" spans="1:3" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="10"/>
+    <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="45"/>
       <c r="B5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="10"/>
+    </row>
+    <row r="6" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="45"/>
+      <c r="B6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="8"/>
+    </row>
+    <row r="7" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="45"/>
+      <c r="B7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="45"/>
+      <c r="B8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="45"/>
+      <c r="B9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="45"/>
+      <c r="B10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="45"/>
+      <c r="B11" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="45"/>
+      <c r="B12" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="45"/>
+      <c r="B13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A14" s="45"/>
+      <c r="B14" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A15" s="45"/>
+      <c r="B15" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" spans="1:3" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="45"/>
+      <c r="B16" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="6"/>
+    </row>
+    <row r="17" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="45"/>
+      <c r="B17" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="6"/>
+    </row>
+    <row r="18" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="45"/>
+      <c r="B18" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="6"/>
+    </row>
+    <row r="19" spans="1:11" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="46"/>
+      <c r="B19" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7"/>
+    </row>
+    <row r="20" spans="1:11" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="34"/>
+      <c r="C20" s="35"/>
+    </row>
+    <row r="21" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="37"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A23" s="37"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A24" s="37"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="37"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="37"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A27" s="37"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:11" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="38"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="4"/>
+    </row>
+    <row r="29" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A29" s="13"/>
+      <c r="B29" s="14"/>
+      <c r="C29" s="15"/>
+    </row>
+    <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:11" ht="21" x14ac:dyDescent="0.25">
+      <c r="A31" s="42" t="s">
+        <v>12</v>
+      </c>
+      <c r="B31" s="43"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="43"/>
+      <c r="G31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="44"/>
+    </row>
+    <row r="32" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
+      <c r="K32" s="28"/>
+    </row>
+    <row r="33" spans="1:11" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="11"/>
-    </row>
-    <row r="6" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="8"/>
-    </row>
-    <row r="7" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="14"/>
-      <c r="B7" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="6"/>
-    </row>
-    <row r="8" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="14"/>
-      <c r="B8" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="6"/>
-    </row>
-    <row r="9" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="6"/>
-    </row>
-    <row r="10" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="6"/>
-    </row>
-    <row r="11" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="6"/>
-    </row>
-    <row r="12" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="6"/>
-    </row>
-    <row r="13" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="6"/>
-    </row>
-    <row r="14" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="6"/>
-    </row>
-    <row r="15" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="6"/>
-    </row>
-    <row r="16" spans="1:3" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A16" s="14"/>
-      <c r="B16" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="6"/>
-    </row>
-    <row r="17" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="14"/>
-      <c r="B18" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="15"/>
-      <c r="B19" s="16" t="s">
+      <c r="D33" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="I33" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="K33" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="7"/>
-    </row>
-    <row r="20" spans="1:11" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="38"/>
-      <c r="C20" s="39"/>
-    </row>
-    <row r="21" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A21" s="40" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2"/>
-    </row>
-    <row r="22" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="41"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A23" s="41"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A24" s="41"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="41"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="41"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="41"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" spans="1:11" ht="23.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="42"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="4"/>
-    </row>
-    <row r="29" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A29" s="17"/>
-      <c r="B29" s="18"/>
-      <c r="C29" s="19"/>
-    </row>
-    <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="31" spans="1:11" ht="21" x14ac:dyDescent="0.3">
-      <c r="A31" s="46" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="47"/>
-      <c r="K31" s="48"/>
-    </row>
-    <row r="32" spans="1:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="32"/>
-    </row>
-    <row r="33" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" s="21" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" s="21" t="s">
+    </row>
+    <row r="34" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D33" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="I33" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="J33" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="K33" s="22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="27"/>
-    </row>
-    <row r="35" spans="1:11" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="34"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="24"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="26"/>
-      <c r="J35" s="26"/>
-      <c r="K35" s="27"/>
-    </row>
-    <row r="36" spans="1:11" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="34"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="24"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="27"/>
-    </row>
-    <row r="37" spans="1:11" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="34"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="24"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="27"/>
-    </row>
-    <row r="38" spans="1:11" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="34"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="26"/>
-      <c r="G38" s="26"/>
-      <c r="H38" s="26"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="27"/>
-    </row>
-    <row r="39" spans="1:11" ht="20.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="35"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="27"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="21"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+      <c r="H34" s="22"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="23"/>
+    </row>
+    <row r="35" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="30"/>
+      <c r="B35" s="24"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+      <c r="H35" s="22"/>
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="23"/>
+    </row>
+    <row r="36" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="30"/>
+      <c r="B36" s="24"/>
+      <c r="C36" s="24"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="23"/>
+    </row>
+    <row r="37" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="30"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="21"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="23"/>
+    </row>
+    <row r="38" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="30"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="22"/>
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="23"/>
+    </row>
+    <row r="39" spans="1:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="31"/>
+      <c r="B39" s="25"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="22"/>
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1308,7 +1280,7 @@
     <mergeCell ref="A21:A28"/>
     <mergeCell ref="B21:B28"/>
     <mergeCell ref="A31:K31"/>
-    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A2:A19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
